--- a/data/availability/projects/horizon-egypt-developments/sa-ada-sahel.xlsx
+++ b/data/availability/projects/horizon-egypt-developments/sa-ada-sahel.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>saada-sahel</t>
+          <t>sa-ada-sahel</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
